--- a/public/数据看板-导出模板.xlsx
+++ b/public/数据看板-导出模板.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>日期</t>
   </si>
@@ -55,7 +55,13 @@
     <t>订单数</t>
   </si>
   <si>
-    <t>产品类型订单分布</t>
+    <t>课程订单总数</t>
+  </si>
+  <si>
+    <t>学习机订单总数</t>
+  </si>
+  <si>
+    <t>会员服务订单总数</t>
   </si>
   <si>
     <t>订单金额</t>
@@ -73,19 +79,10 @@
     <t>预估收入</t>
   </si>
   <si>
-    <t>课程</t>
-  </si>
-  <si>
-    <t>学习机</t>
-  </si>
-  <si>
-    <t>会员服务</t>
-  </si>
-  <si>
-    <t>超量导出</t>
-  </si>
-  <si>
-    <t>批量查看</t>
+    <t>超量导出次数</t>
+  </si>
+  <si>
+    <t>批量查看次数</t>
   </si>
 </sst>
 </file>
@@ -731,8 +728,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1051,8 +1048,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="18.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.125" style="2" customWidth="1"/>
@@ -1061,8 +1058,9 @@
     <col min="5" max="5" width="21.25" style="2" customWidth="1"/>
     <col min="6" max="7" width="26.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="9" style="2"/>
-    <col min="9" max="9" width="11.625" style="2" customWidth="1"/>
-    <col min="10" max="11" width="9" style="2"/>
+    <col min="9" max="9" width="18.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.625" style="2" customWidth="1"/>
     <col min="12" max="12" width="10.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="12.125" style="2" customWidth="1"/>
     <col min="14" max="14" width="15" style="2" customWidth="1"/>
@@ -1097,64 +1095,96 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="R1" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>18</v>
+      <c r="A2" s="6">
+        <v>45799</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>286</v>
+      </c>
+      <c r="D2" s="2">
+        <v>122</v>
+      </c>
+      <c r="E2" s="2">
+        <v>286</v>
+      </c>
+      <c r="F2" s="2">
+        <v>194</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="2">
+        <v>200</v>
+      </c>
+      <c r="I2" s="2">
+        <v>200</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>19000</v>
+      </c>
+      <c r="M2" s="2">
+        <v>9000</v>
+      </c>
+      <c r="N2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="P2" s="2">
+        <v>4000</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="6">
-        <v>45799</v>
+        <v>45798</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1208,80 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="6">
-        <v>45798</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>286</v>
-      </c>
-      <c r="D4" s="2">
-        <v>122</v>
-      </c>
-      <c r="E4" s="2">
-        <v>286</v>
-      </c>
-      <c r="F4" s="2">
-        <v>194</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="2">
-        <v>200</v>
-      </c>
-      <c r="I4" s="2">
-        <v>200</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>19000</v>
-      </c>
-      <c r="M4" s="2">
-        <v>9000</v>
-      </c>
-      <c r="N4" s="2">
-        <v>5000</v>
-      </c>
-      <c r="O4" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="P4" s="2">
-        <v>4000</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>1</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
